--- a/InputData/trans/ANVCV/Additional New Vehicles Calibration Variable.xlsx
+++ b/InputData/trans/ANVCV/Additional New Vehicles Calibration Variable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\trans\ANVCV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\trans\ANVCV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C65778-ACE1-4F90-8235-4F800CB7F99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AA3D02-1D62-4397-9ABC-9D0B34CD31F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="2100" windowWidth="24420" windowHeight="14370" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -163,6 +163,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="About"/>
@@ -548,36 +549,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="101.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -592,99 +593,111 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="1" max="5" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="C1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="D1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="E1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="F1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="G1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="H1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="I1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="J1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="K1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="L1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="M1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="N1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="O1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="P1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="Q1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="R1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="S1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="T1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="U1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="V1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="W1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="X1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="Y1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="Z1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AA1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AB1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -769,8 +782,20 @@
       <c r="AB2">
         <v>0</v>
       </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -855,8 +880,20 @@
       <c r="AB3">
         <v>0</v>
       </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -941,8 +978,20 @@
       <c r="AB4">
         <v>0</v>
       </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1027,8 +1076,20 @@
       <c r="AB5">
         <v>0</v>
       </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1113,8 +1174,20 @@
       <c r="AB6">
         <v>0</v>
       </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1197,6 +1270,18 @@
         <v>0</v>
       </c>
       <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>0</v>
       </c>
     </row>
@@ -1210,99 +1295,111 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="1" max="5" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="C1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="D1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="E1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="F1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="G1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="H1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="I1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="J1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="K1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="L1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="M1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="N1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="O1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="P1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="Q1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="R1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="S1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="T1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="U1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="V1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="W1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="X1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="Y1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="Z1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AA1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AB1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1387,8 +1484,20 @@
       <c r="AB2">
         <v>0</v>
       </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1473,8 +1582,20 @@
       <c r="AB3">
         <v>0</v>
       </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1559,8 +1680,20 @@
       <c r="AB4">
         <v>0</v>
       </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1645,8 +1778,20 @@
       <c r="AB5">
         <v>0</v>
       </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1731,8 +1876,20 @@
       <c r="AB6">
         <v>0</v>
       </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1815,6 +1972,18 @@
         <v>0</v>
       </c>
       <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>0</v>
       </c>
     </row>
